--- a/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="461">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,10 +319,10 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -358,7 +358,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」</t>
+    <t>リソースコンテンツの言語</t>
   </si>
   <si>
     <t>リソースが書かれている基本言語。</t>
@@ -370,7 +370,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」</t>
+    <t>人間の言語。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -416,7 +416,7 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」</t>
+    <t>含まれている、インラインのリソース</t>
   </si>
   <si>
     <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
@@ -461,7 +461,7 @@
     <t>ImagingStudy.modifierExtension</t>
   </si>
   <si>
-    <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
+    <t>無視できない拡張機能</t>
   </si>
   <si>
     <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
@@ -490,7 +490,7 @@
     <t>DICOMスタディインスタンスUIDやアクセッション番号などのImagingStudyの識別子。</t>
   </si>
   <si>
-    <t>DICOMスタディインスタンスUIDのエンコードについては、[Imaging Study Implementation Notes]（imagingstudy.html＃notes）の説明を参照。アクセッション番号はACSN識別子タイプを使用する必要がある。  
+    <t>DICOMスタディインスタンスUIDのエンコードについては、[Imaging Study Implementation Notes]（imagingstudy.html#notes）の説明を参照。アクセッション番号はACSN識別子タイプを使用する必要がある。  
 【JP-Core仕様】Study Instance UIDは画像が存在する場合に必須、その他は任意。StudyInstanceUID (0020,000D)</t>
   </si>
   <si>
@@ -512,7 +512,7 @@
     <t>ImagingStudy.status</t>
   </si>
   <si>
-    <t>"登録済み | 利用可能 | 取消済み | エラーで入力 | 不明" (Tōrokuzumi | Riyō kanō | Torikeshi zumi | Erā de nyūryoku | Fumei)</t>
+    <t>登録済み | 利用可能 | 取消済み | エラーで入力 | 不明</t>
   </si>
   <si>
     <t>ImagingStudyの現在のステータス</t>
@@ -560,18 +560,12 @@
     <t>実際の取得モダリティであるすべてのseries.modality値のリスト、つまりDICOMコンテキストグループ29（値セットOID 1.2.840.10008.6.1.19）の値。</t>
   </si>
   <si>
-    <t>コードは、列挙型またはコードリストで、SNOMED CTなどの非常に正式な定義まで、非常にカジュアルに定義できる。詳細については、HL7v3コア原則を参照のこと。  
+    <t>コードは、列挙型またはコードリストで、DICOMのモダリティコードを利用する。  
 ・モダリティのコードを設定。  
 ・Seriesの階層の(0008,0060)を集約する、または(0008,0060)　と　(0008, 0061) のOR。但し、重複する値は1つにまとめて表現。</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>インスタンスにおける取得データの種類。</t>
-  </si>
-  <si>
-    <t>http://dicom.nema.org/medical/dicom/current/output/chtml/part16/sect_CID_29.html</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
   </si>
   <si>
     <t>.code</t>
@@ -1152,11 +1146,9 @@
     <t>シリーズが取得されたモダリティー</t>
   </si>
   <si>
-    <t>コードは、列挙型またはコードリストで、SNOMED CTなどの非常に正式な定義まで、非常に柔軟に定義できる。ただしJP CoreではSNOMED CTを推奨しない。詳細については、HL7v3コア原則を参照。  
-当該シリーズのモダリティコード。1シリーズ1モダリティ（1つのシリーズの中に複数のモダリティが混在することはない）。  
-（参照先）  
-ftp://medical.nema.org/medical/dicom/resources/valuesets/fhir/json/CID_29.json  
-https://dicom.nema.org/medical/dicom/current/output/chtml/part16/sect_CID_29.html</t>
+    <t>JP CoreではDICOMのモダリティコードを利用する。SNOMED CTは推奨しない。  
+（参照先）   
+http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS.html</t>
   </si>
   <si>
     <t>(0008,0060)</t>
@@ -1192,7 +1184,7 @@
 </t>
   </si>
   <si>
-    <t>"シリーズ関連インスタンスの数" (Shirīzu kanren insutansu no kazu)</t>
+    <t>シリーズ関連インスタンスの数</t>
   </si>
   <si>
     <t>32ビット数で表す。これより大きい値の場合は、10進数を使用する。  
@@ -1235,10 +1227,7 @@
     <t>コードは、列挙型またはコードリストで、どの部位の検査なのかを示す。フリーではなく、DICOM定義書の中で示される語句（コード）をデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
   </si>
   <si>
-    <t>DICOM tagに設定されているコードをデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1349,13 +1338,16 @@
     <t>ImagingStudy.series.performer.function</t>
   </si>
   <si>
-    <t>「パフォーマンスの種類」</t>
-  </si>
-  <si>
-    <t>"俳優のシリーズへの参加のタイプを区別する。"</t>
+    <t>パフォーマンスの種類</t>
+  </si>
+  <si>
+    <t>俳優のシリーズへの参加のタイプを区別する。</t>
   </si>
   <si>
     <t>Allows disambiguation of the types of involvement of different performers.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>パフォーマーの関与のタイプ</t>
@@ -1371,7 +1363,7 @@
 </t>
   </si>
   <si>
-    <t>"シリーズを演奏したのは誰ですか。" (Shirīzu o ensō shita no wa dare desu ka.)</t>
+    <t>シリーズを演奏したのは誰ですか。</t>
   </si>
   <si>
     <t>シリーズを行った人または物を示す。</t>
@@ -1455,10 +1447,7 @@
     <t>【JP Core仕様】SOPクラスUID。DICOMタグマッピングにある値をそのまま設定。</t>
   </si>
   <si>
-    <t>インスタンスのSOPクラス。</t>
-  </si>
-  <si>
-    <t>http://dicom.nema.org/medical/dicom/current/output/chtml/part04/sect_B.5.html#table_B.5-1</t>
+    <t>http://hl7.org/fhir/uv/imaging-service-request-ig/ValueSet/dicom-sop-classes</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP]. source[classCode=OBS, moodCode=EVN, code="sop class"].value</t>
@@ -1477,7 +1466,7 @@
     <t>このシリーズにおけるこのインスタンスの番号</t>
   </si>
   <si>
-    <t>シリーズ内のインスタンスの数。 (Shirīzu-nai no insutansu no kazu.)</t>
+    <t>シリーズ内のインスタンスの数。</t>
   </si>
   <si>
     <t>32ビット数で表す。これより大きい値の場合は、10進数を使用する。  
@@ -1853,7 +1842,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="133.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="87.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.15234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -3345,13 +3334,11 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Y13" s="2"/>
+      <c r="Z13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3387,13 +3374,13 @@
         <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3401,10 +3388,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3427,16 +3414,16 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3486,7 +3473,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>90</v>
@@ -3501,16 +3488,16 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3518,10 +3505,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3544,16 +3531,16 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3603,7 +3590,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3618,16 +3605,16 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -3635,14 +3622,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3661,16 +3648,16 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3684,7 +3671,7 @@
         <v>79</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>79</v>
@@ -3720,7 +3707,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3735,16 +3722,16 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>79</v>
@@ -3752,10 +3739,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3778,19 +3765,19 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3839,7 +3826,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3854,16 +3841,16 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3871,14 +3858,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3897,16 +3884,16 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3956,7 +3943,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3974,13 +3961,13 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -3988,14 +3975,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4014,16 +4001,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4073,7 +4060,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4091,13 +4078,13 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4105,10 +4092,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4131,19 +4118,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4192,7 +4179,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4210,7 +4197,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4224,14 +4211,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4250,16 +4237,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4309,7 +4296,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4327,10 +4314,10 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>79</v>
@@ -4341,14 +4328,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4367,16 +4354,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4426,7 +4413,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4444,10 +4431,10 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>79</v>
@@ -4458,10 +4445,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4484,16 +4471,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4543,7 +4530,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4558,13 +4545,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>79</v>
@@ -4575,14 +4562,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4601,16 +4588,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4636,13 +4623,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4660,7 +4647,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4675,13 +4662,13 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -4692,10 +4679,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4718,19 +4705,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4779,7 +4766,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4794,27 +4781,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>282</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4837,16 +4824,16 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4872,14 +4859,14 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Y26" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4896,7 +4883,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4911,16 +4898,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4928,10 +4915,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4954,16 +4941,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5013,7 +5000,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5028,27 +5015,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>301</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5071,16 +5058,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5130,7 +5117,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5145,10 +5132,10 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -5162,14 +5149,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5188,16 +5175,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5247,7 +5234,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5265,10 +5252,10 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
@@ -5279,10 +5266,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5305,16 +5292,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5364,7 +5351,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5382,7 +5369,7 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5396,10 +5383,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5422,13 +5409,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5479,7 +5466,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5497,7 +5484,7 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5511,10 +5498,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5543,7 +5530,7 @@
         <v>137</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>139</v>
@@ -5596,7 +5583,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5614,7 +5601,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5628,14 +5615,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5657,10 +5644,10 @@
         <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>139</v>
@@ -5715,7 +5702,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5747,14 +5734,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5776,16 +5763,16 @@
         <v>92</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5798,7 +5785,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5834,7 +5821,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>90</v>
@@ -5852,10 +5839,10 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
@@ -5866,14 +5853,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5892,16 +5879,16 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5915,7 +5902,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -5951,7 +5938,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5969,10 +5956,10 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5983,14 +5970,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6012,13 +5999,13 @@
         <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6044,14 +6031,12 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Y36" s="2"/>
+      <c r="Z36" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Y36" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>177</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6068,7 +6053,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>90</v>
@@ -6086,10 +6071,10 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -6100,14 +6085,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6126,16 +6111,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6149,7 +6134,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6185,7 +6170,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6203,10 +6188,10 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6217,14 +6202,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6243,16 +6228,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6302,7 +6287,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6320,10 +6305,10 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6334,10 +6319,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6360,19 +6345,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6421,7 +6406,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6439,7 +6424,7 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6453,14 +6438,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6482,13 +6467,13 @@
         <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6514,13 +6499,11 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6538,7 +6521,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6556,10 +6539,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6570,10 +6553,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6599,13 +6582,13 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6631,13 +6614,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6655,7 +6638,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6673,10 +6656,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6687,10 +6670,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6713,16 +6696,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6772,7 +6755,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6790,10 +6773,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6804,10 +6787,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6830,16 +6813,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6889,7 +6872,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6907,10 +6890,10 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6921,14 +6904,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6947,19 +6930,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7008,7 +6991,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7023,13 +7006,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -7040,10 +7023,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7066,13 +7049,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7123,7 +7106,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7141,7 +7124,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7155,10 +7138,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7187,7 +7170,7 @@
         <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7240,7 +7223,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7258,7 +7241,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7272,14 +7255,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7301,10 +7284,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -7359,7 +7342,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7391,10 +7374,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7417,17 +7400,17 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7452,13 +7435,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>175</v>
+        <v>414</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7476,7 +7459,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7494,7 +7477,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7508,10 +7491,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7534,16 +7517,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7593,7 +7576,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7611,24 +7594,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>426</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7651,16 +7634,16 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7710,7 +7693,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7728,7 +7711,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7742,10 +7725,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7768,13 +7751,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7825,7 +7808,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7843,7 +7826,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7857,10 +7840,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7889,7 +7872,7 @@
         <v>137</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>139</v>
@@ -7942,7 +7925,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7960,7 +7943,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7974,14 +7957,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8003,10 +7986,10 @@
         <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>139</v>
@@ -8061,7 +8044,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8093,14 +8076,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8122,16 +8105,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8144,7 +8127,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8180,7 +8163,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8198,10 +8181,10 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8212,14 +8195,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8241,13 +8224,13 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8273,13 +8256,11 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8297,7 +8278,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8315,10 +8296,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8329,14 +8310,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8355,16 +8336,16 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8414,7 +8395,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8432,10 +8413,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8446,10 +8427,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8472,16 +8453,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8531,7 +8512,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8549,10 +8530,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -455,7 +455,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ImagingStudy.modifierExtension</t>
@@ -1227,7 +1227,10 @@
     <t>コードは、列挙型またはコードリストで、どの部位の検査なのかを示す。フリーではなく、DICOM定義書の中で示される語句（コード）をデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS</t>
+    <t>DICOM tagに設定されているコードをデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1341,7 +1344,7 @@
     <t>パフォーマンスの種類</t>
   </si>
   <si>
-    <t>俳優のシリーズへの参加のタイプを区別する。</t>
+    <t>実施者・撮影者のシリーズへの参加のタイプを区別する。</t>
   </si>
   <si>
     <t>Allows disambiguation of the types of involvement of different performers.</t>
@@ -1363,7 +1366,7 @@
 </t>
   </si>
   <si>
-    <t>シリーズを演奏したのは誰ですか。</t>
+    <t>シリーズを実施・撮影したのは誰ですか。</t>
   </si>
   <si>
     <t>シリーズを行った人または物を示す。</t>
@@ -6501,9 +6504,11 @@
       <c r="X40" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="Y40" s="2"/>
+      <c r="Y40" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="Z40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6539,10 +6544,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6553,10 +6558,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6582,13 +6587,13 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6617,10 +6622,10 @@
         <v>285</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6638,7 +6643,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6656,10 +6661,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6670,10 +6675,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6696,16 +6701,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6755,7 +6760,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6773,10 +6778,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6787,10 +6792,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6816,13 +6821,13 @@
         <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6872,7 +6877,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6893,7 +6898,7 @@
         <v>204</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6904,14 +6909,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6933,16 +6938,16 @@
         <v>316</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6991,7 +6996,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7006,13 +7011,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>228</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -7023,10 +7028,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7138,10 +7143,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7255,10 +7260,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7374,10 +7379,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7403,14 +7408,14 @@
         <v>263</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7435,13 +7440,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7459,7 +7464,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7491,10 +7496,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7517,16 +7522,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7576,7 +7581,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7594,24 +7599,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7637,13 +7642,13 @@
         <v>316</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7693,7 +7698,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7711,7 +7716,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7725,10 +7730,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7840,10 +7845,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7957,10 +7962,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8076,14 +8081,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8105,16 +8110,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8127,7 +8132,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8163,7 +8168,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8184,7 +8189,7 @@
         <v>340</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8195,14 +8200,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8224,13 +8229,13 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8256,11 +8261,11 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8278,7 +8283,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8296,10 +8301,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8310,14 +8315,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8339,13 +8344,13 @@
         <v>240</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8395,7 +8400,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8413,10 +8418,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8427,10 +8432,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8456,13 +8461,13 @@
         <v>309</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8512,7 +8517,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8530,10 +8535,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -1820,17 +1820,17 @@
   <dimension ref="A1:AO57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.81640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.81640625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.13671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.13671875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="220.078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1839,27 +1839,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="59.36328125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="133.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.15234375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.37890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="50.890625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="114.3125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.0" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.90234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="114.25" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="104.890625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="28.1484375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="97.94921875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="89.92578125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="24.1328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -373,7 +373,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -673,7 +673,7 @@
     <t>ImagingStudy.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|Appointment|AppointmentResponse|Task)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|Appointment|4.0.1|AppointmentResponse|4.0.1|Task|4.0.1)
 </t>
   </si>
   <si>
@@ -752,7 +752,7 @@
     <t>ImagingStudy.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -881,7 +881,7 @@
     <t>ImagingStudy.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -932,7 +932,7 @@
     <t>研究の理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1264,7 +1264,7 @@
     <t>ImagingStudy.series.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1356,7 +1356,7 @@
     <t>パフォーマーの関与のタイプ</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/series-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/series-performer-function|4.0.1</t>
   </si>
   <si>
     <t>ImagingStudy.series.performer.actor</t>

--- a/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
